--- a/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_AttenuatorDaughterboard_V1_031426/T41-RF-board-AttenuatorDaughterBoard-Assy_BOM.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_AttenuatorDaughterboard_V1_031426/T41-RF-board-AttenuatorDaughterBoard-Assy_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_AttenuatorDaughterboard_V1_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3400869C-820F-4776-86B8-98F2D019B835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326C4651-42B7-4815-86B4-EFB6373F6491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E6C0461D-248E-4A4E-92B0-0B75F2E9898F}"/>
   </bookViews>
@@ -85,7 +85,7 @@
     <t>0603</t>
   </si>
   <si>
-    <t>C1002</t>
+    <t>C1149515</t>
   </si>
 </sst>
 </file>
